--- a/data/trans_orig/P37C2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P37C2_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la creencia de que las vacunas son seguras en 2023</t>
+          <t>Población según la creencia de que las vacunas son seguras en 2023 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>11412</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>14039</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12240</t>
+          <t>12433</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29937</t>
+          <t>29801</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>22404</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23927</t>
+          <t>23052</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47626</t>
+          <t>44518</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66579</t>
+          <t>67128</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102644</t>
+          <t>101449</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57941</t>
+          <t>58184</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84157</t>
+          <t>83605</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>129931</t>
+          <t>132030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174046</t>
+          <t>175257</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>372460</t>
+          <t>371800</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410876</t>
+          <t>410242</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>345007</t>
+          <t>345396</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>374122</t>
+          <t>374832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>731462</t>
+          <t>728951</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>780216</t>
+          <t>776477</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,66%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>11566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11242</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>13152</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29980</t>
+          <t>30068</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27766</t>
+          <t>28658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>26776</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50612</t>
+          <t>50741</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63955</t>
+          <t>64849</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95553</t>
+          <t>95558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64863</t>
+          <t>66536</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92095</t>
+          <t>93601</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139112</t>
+          <t>139111</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>181169</t>
+          <t>181513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>329918</t>
+          <t>329036</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>364290</t>
+          <t>364409</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>262812</t>
+          <t>264700</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>293770</t>
+          <t>294495</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>599109</t>
+          <t>601322</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>647996</t>
+          <t>648858</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,07%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8619</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13650</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14571</t>
+          <t>14998</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>64086</t>
+          <t>65770</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17882</t>
+          <t>18756</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>68785</t>
+          <t>70775</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28913</t>
+          <t>32702</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>152501</t>
+          <t>153358</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25056</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41570</t>
+          <t>42686</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48473</t>
+          <t>50884</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>183962</t>
+          <t>186940</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>437403</t>
+          <t>437459</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>620682</t>
+          <t>614107</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>110831</t>
+          <t>110216</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>129344</t>
+          <t>128790</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>564801</t>
+          <t>559770</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>758500</t>
+          <t>753792</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>809</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20232</t>
+          <t>21713</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6462</t>
+          <t>6509</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23818</t>
+          <t>24051</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30824</t>
+          <t>32102</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>58037</t>
+          <t>58837</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13642</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>39474</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>48732</t>
+          <t>48503</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>87842</t>
+          <t>89815</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>209487</t>
+          <t>210381</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>271525</t>
+          <t>271046</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67921</t>
+          <t>81222</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>194425</t>
+          <t>195394</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>271311</t>
+          <t>280166</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>448563</t>
+          <t>446884</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>694586</t>
+          <t>699018</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>761764</t>
+          <t>763821</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>737728</t>
+          <t>736667</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>889487</t>
+          <t>874858</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1451925</t>
+          <t>1453597</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1669613</t>
+          <t>1660362</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>82,96%</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>299</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>553</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8366</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15034</t>
+          <t>15719</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10991</t>
+          <t>11114</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>23020</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25326</t>
+          <t>25879</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>54039</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>30308</t>
+          <t>31120</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>60653</t>
+          <t>62545</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>61523</t>
+          <t>61228</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>104257</t>
+          <t>102779</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>87935</t>
+          <t>85040</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>124551</t>
+          <t>124328</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>153981</t>
+          <t>150363</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>381688</t>
+          <t>371118</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>256839</t>
+          <t>257566</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>508662</t>
+          <t>518201</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,7%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>297759</t>
+          <t>297110</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>339395</t>
+          <t>339950</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>423052</t>
+          <t>419517</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>627452</t>
+          <t>630358</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>729822</t>
+          <t>715731</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>950089</t>
+          <t>950209</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,79%</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>527</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>10623</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>37352</t>
+          <t>39085</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>30107</t>
+          <t>29238</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>58826</t>
+          <t>58177</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>43117</t>
+          <t>44241</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>81463</t>
+          <t>83568</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>39615</t>
+          <t>40636</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>83900</t>
+          <t>83270</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>138600</t>
+          <t>138586</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>181411</t>
+          <t>179664</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>191590</t>
+          <t>193991</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>249092</t>
+          <t>256150</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>127763</t>
+          <t>126492</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>176205</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>523680</t>
+          <t>526412</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>570811</t>
+          <t>569904</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>666973</t>
+          <t>656069</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>732713</t>
+          <t>727371</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>23088</t>
+          <t>22694</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>20457</t>
+          <t>22067</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>14842</t>
+          <t>13818</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>37292</t>
+          <t>35379</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>23329</t>
+          <t>24664</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>48382</t>
+          <t>49508</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>26302</t>
+          <t>26682</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>39410</t>
+          <t>40760</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>67665</t>
+          <t>70023</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>134704</t>
+          <t>134739</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>211491</t>
+          <t>212845</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>119946</t>
+          <t>120671</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>177514</t>
+          <t>178181</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>277632</t>
+          <t>277097</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>366999</t>
+          <t>370005</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>514923</t>
+          <t>500507</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>736559</t>
+          <t>735368</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>600534</t>
+          <t>602018</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>881847</t>
+          <t>897893</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1199365</t>
+          <t>1203894</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1549328</t>
+          <t>1548242</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2378672</t>
+          <t>2377196</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2690319</t>
+          <t>2692211</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2509395</t>
+          <t>2514460</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2805166</t>
+          <t>2800153</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4956983</t>
+          <t>4959096</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5345464</t>
+          <t>5354052</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37C2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P37C2_2023-Clase-trans_orig.xlsx
@@ -725,59 +725,59 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3965</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3716</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12522</t>
+          <t>11404</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19336</t>
+          <t>20918</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>13387</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29801</t>
+          <t>30976</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>23494</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>36166</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>25545</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44518</t>
+          <t>49805</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83212</t>
+          <t>91909</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67128</t>
+          <t>75087</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101449</t>
+          <t>111471</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>69648</t>
+          <t>77075</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58184</t>
+          <t>63329</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83605</t>
+          <t>91121</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>152860</t>
+          <t>168984</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>132030</t>
+          <t>147498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175257</t>
+          <t>192399</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>392617</t>
+          <t>427518</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>371800</t>
+          <t>407031</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410242</t>
+          <t>448255</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>361124</t>
+          <t>392187</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>345396</t>
+          <t>377205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>374832</t>
+          <t>407481</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>753741</t>
+          <t>819705</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>728951</t>
+          <t>793266</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>776477</t>
+          <t>843228</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,31%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>504040</t>
+          <t>549430</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>504040</t>
+          <t>549430</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>504040</t>
+          <t>549430</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>446770</t>
+          <t>487665</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>446770</t>
+          <t>487665</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>446770</t>
+          <t>487665</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>950810</t>
+          <t>1037095</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>950810</t>
+          <t>1037095</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>950810</t>
+          <t>1037095</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>13654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>11737</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19836</t>
+          <t>21687</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30068</t>
+          <t>32425</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>19278</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>12969</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28658</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>37227</t>
+          <t>40965</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26776</t>
+          <t>29368</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50741</t>
+          <t>54506</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79397</t>
+          <t>86840</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64849</t>
+          <t>70155</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95558</t>
+          <t>104433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>78818</t>
+          <t>89218</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66536</t>
+          <t>74830</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93601</t>
+          <t>104446</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>158215</t>
+          <t>176058</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139111</t>
+          <t>155037</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>181513</t>
+          <t>201167</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>347855</t>
+          <t>368992</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>329036</t>
+          <t>351141</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>364409</t>
+          <t>387900</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>279219</t>
+          <t>305941</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>264700</t>
+          <t>289436</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>294495</t>
+          <t>321887</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>627074</t>
+          <t>674932</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>601322</t>
+          <t>650290</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>648858</t>
+          <t>699164</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>450492</t>
+          <t>481109</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>450492</t>
+          <t>481109</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>450492</t>
+          <t>481109</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>380605</t>
+          <t>420238</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>380605</t>
+          <t>420238</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>380605</t>
+          <t>420238</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>831097</t>
+          <t>901347</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>831097</t>
+          <t>901347</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>831097</t>
+          <t>901347</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,67 +2089,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8048</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9160</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>9064</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2177</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8121</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>12567</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>646</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14998</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>36795</t>
+          <t>38653</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12365</t>
+          <t>27320</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65770</t>
+          <t>52735</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8003</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>5143</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>14243</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>44798</t>
+          <t>47681</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>35778</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>70775</t>
+          <t>62520</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>92280</t>
+          <t>104865</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32702</t>
+          <t>89125</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>153358</t>
+          <t>124548</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33282</t>
+          <t>37778</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26101</t>
+          <t>29674</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42686</t>
+          <t>47571</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>125562</t>
+          <t>142643</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50884</t>
+          <t>123853</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>186940</t>
+          <t>166264</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>526664</t>
+          <t>312665</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>437459</t>
+          <t>289326</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>614107</t>
+          <t>331673</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>120763</t>
+          <t>135688</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>110216</t>
+          <t>125422</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128790</t>
+          <t>145404</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>647427</t>
+          <t>448353</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>559770</t>
+          <t>422839</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>753792</t>
+          <t>470681</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>664648</t>
+          <t>467733</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>664648</t>
+          <t>467733</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>664648</t>
+          <t>467733</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>164888</t>
+          <t>185496</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>164888</t>
+          <t>185496</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>164888</t>
+          <t>185496</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>829536</t>
+          <t>653229</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>829536</t>
+          <t>653229</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>829536</t>
+          <t>653229</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>828</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>12095</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12467</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21713</t>
+          <t>23822</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6509</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>15333</t>
+          <t>17254</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>10559</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24051</t>
+          <t>25633</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>43478</t>
+          <t>49293</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32102</t>
+          <t>35653</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>58837</t>
+          <t>66531</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>27076</t>
+          <t>33011</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13089</t>
+          <t>24760</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39474</t>
+          <t>43997</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>70555</t>
+          <t>82304</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>48503</t>
+          <t>66322</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>89815</t>
+          <t>106395</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>239131</t>
+          <t>267557</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>210381</t>
+          <t>238357</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>271046</t>
+          <t>298527</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>148938</t>
+          <t>162306</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>81222</t>
+          <t>145091</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>195394</t>
+          <t>184674</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>388069</t>
+          <t>429863</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>280166</t>
+          <t>393025</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>446884</t>
+          <t>464730</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>730718</t>
+          <t>790764</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>699018</t>
+          <t>757261</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>763821</t>
+          <t>824480</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>792393</t>
+          <t>654575</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>736667</t>
+          <t>630055</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>874858</t>
+          <t>673747</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1523112</t>
+          <t>1445339</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1453597</t>
+          <t>1404868</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1660362</t>
+          <t>1483548</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>74,92%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1026639</t>
+          <t>1122565</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1026639</t>
+          <t>1122565</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1026639</t>
+          <t>1122565</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>974719</t>
+          <t>857722</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>974719</t>
+          <t>857722</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>974719</t>
+          <t>857722</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2001359</t>
+          <t>1980287</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2001359</t>
+          <t>1980287</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2001359</t>
+          <t>1980287</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1644</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>432</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>855</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15719</t>
+          <t>17506</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,67 +3601,67 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>14820</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>9026</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>23838</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>13798</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>8390</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>23020</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>36443</t>
+          <t>51076</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25879</t>
+          <t>37545</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>54039</t>
+          <t>68568</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>42869</t>
+          <t>42894</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31120</t>
+          <t>32523</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>62545</t>
+          <t>55340</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>79312</t>
+          <t>93970</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>61228</t>
+          <t>76317</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>102779</t>
+          <t>114385</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>105644</t>
+          <t>126080</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>85040</t>
+          <t>107231</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>124328</t>
+          <t>150006</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>215958</t>
+          <t>171758</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>150363</t>
+          <t>151556</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>371118</t>
+          <t>191221</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>321603</t>
+          <t>297838</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>257566</t>
+          <t>271070</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>518201</t>
+          <t>328967</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>318744</t>
+          <t>369405</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>297110</t>
+          <t>344070</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>339950</t>
+          <t>393675</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>569445</t>
+          <t>604068</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>419517</t>
+          <t>581867</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>630358</t>
+          <t>625499</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>888188</t>
+          <t>973473</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>715731</t>
+          <t>940115</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>950209</t>
+          <t>1005196</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,69%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>470452</t>
+          <t>557065</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>470452</t>
+          <t>557065</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>470452</t>
+          <t>557065</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>834929</t>
+          <t>825863</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>834929</t>
+          <t>825863</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>834929</t>
+          <t>825863</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1305381</t>
+          <t>1382928</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1305381</t>
+          <t>1382928</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1305381</t>
+          <t>1382928</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>541</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>11619</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>711</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,22 +4283,22 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4497</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>19631</t>
+          <t>19472</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8797</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>39085</t>
+          <t>38592</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>40903</t>
+          <t>44543</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>29238</t>
+          <t>32555</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>58177</t>
+          <t>61669</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>60534</t>
+          <t>64015</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>44241</t>
+          <t>47763</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>83568</t>
+          <t>90114</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>60522</t>
+          <t>67630</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>40636</t>
+          <t>46607</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>83270</t>
+          <t>90371</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>159470</t>
+          <t>178827</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>138586</t>
+          <t>157893</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>179664</t>
+          <t>201327</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>219992</t>
+          <t>246457</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>193991</t>
+          <t>217156</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>256150</t>
+          <t>281716</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>152546</t>
+          <t>142586</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>126492</t>
+          <t>118636</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>165213</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>547272</t>
+          <t>608044</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>526412</t>
+          <t>583013</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>569904</t>
+          <t>630686</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>699819</t>
+          <t>750630</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>656069</t>
+          <t>710932</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>727371</t>
+          <t>783528</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,29%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>235338</t>
+          <t>231881</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>235338</t>
+          <t>231881</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>235338</t>
+          <t>231881</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>753081</t>
+          <t>837141</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>753081</t>
+          <t>837141</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>753081</t>
+          <t>837141</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>988419</t>
+          <t>1069022</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>988419</t>
+          <t>1069022</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>988419</t>
+          <t>1069022</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,67 +4817,67 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>22694</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>13024</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>23441</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>11195</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>5899</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>22067</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>23251</t>
+          <t>24404</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>35379</t>
+          <t>38007</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>34703</t>
+          <t>40493</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>24664</t>
+          <t>28991</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>49508</t>
+          <t>54455</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>19636</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>12927</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>26682</t>
+          <t>28318</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>52830</t>
+          <t>60129</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>40760</t>
+          <t>46974</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>70023</t>
+          <t>76683</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>175520</t>
+          <t>201100</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>134739</t>
+          <t>170671</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>212845</t>
+          <t>235003</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>149338</t>
+          <t>164001</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>120671</t>
+          <t>142448</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>178181</t>
+          <t>186498</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>324858</t>
+          <t>365101</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>277097</t>
+          <t>326682</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>370005</t>
+          <t>406742</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>660186</t>
+          <t>744881</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>500507</t>
+          <t>698106</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>735368</t>
+          <t>808221</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,67 +5191,67 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>706115</t>
+          <t>716961</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>602018</t>
+          <t>678272</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>897893</t>
+          <t>757968</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
+          <t>19,84%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>18,77%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>20,97%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>1461842</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>1395248</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>1534378</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>20,81%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
           <t>19,86%</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>16,93%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>25,26%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>1804</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>1366301</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>1203894</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>1548242</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>19,78%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>17,43%</t>
-        </is>
-      </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2469144</t>
+          <t>2411929</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2377196</t>
+          <t>2347623</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2692211</t>
+          <t>2470901</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2670217</t>
+          <t>2700502</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2514460</t>
+          <t>2656171</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2800153</t>
+          <t>2744307</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>5139361</t>
+          <t>5112431</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4959096</t>
+          <t>5023819</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5354052</t>
+          <t>5182544</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>73,78%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3351609</t>
+          <t>3409783</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3351609</t>
+          <t>3409783</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3351609</t>
+          <t>3409783</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3554992</t>
+          <t>3614124</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3554992</t>
+          <t>3614124</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3554992</t>
+          <t>3614124</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>6906601</t>
+          <t>7023907</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6906601</t>
+          <t>7023907</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6906601</t>
+          <t>7023907</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
